--- a/registry.xlsx
+++ b/registry.xlsx
@@ -1883,7 +1883,7 @@
     <row r="1" ht="23.85" customHeight="1" s="5">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="2" ht="12.8" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>PRJ-001</t>
+          <t>C1-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="3" ht="12.8" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>PRJ-002</t>
+          <t>C1-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="1" ht="23.85" customHeight="1" s="5">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>c1_human_id</t>
+          <t>c1_id</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
     <row r="2" ht="12.8" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>PRJ-001</t>
+          <t>C1-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>APP-001</t>
+          <t>C2-001</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="3" ht="12.8" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>PRJ-999</t>
+          <t>C1-999</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>APP-ORPH-1</t>
+          <t>C2-ORPH-1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="1" ht="23.85" customHeight="1" s="5">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>c2_human_id</t>
+          <t>c2_id</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="2" ht="12.8" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>APP-001</t>
+          <t>C2-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>CMP-001</t>
+          <t>C3-001</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -2514,12 +2514,12 @@
     <row r="3" ht="12.8" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>APP-999</t>
+          <t>C2-999</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CMP-ORPH-1</t>
+          <t>C3-ORPH-1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2613,12 +2613,12 @@
     <row r="1" ht="23.85" customHeight="1" s="5">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>c3_human_id</t>
+          <t>c3_id</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>human_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -2705,12 +2705,12 @@
     <row r="2" ht="12.8" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CMP-001</t>
+          <t>C3-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>RUN-001</t>
+          <t>C4-001</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="3" ht="12.8" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CMP-999</t>
+          <t>C3-999</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>RUN-ORPH-1</t>
+          <t>C4-ORPH-1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
